--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44529</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45237</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43609</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>43976</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44019</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44033</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44279</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44602</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44806</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44827</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44840</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44908</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44930</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44966</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44986</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45107</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45237</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>43437</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>43535</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43703</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43705</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>43784</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43812</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44033</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44053</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44293</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44776</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44792</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44791</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44826</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44842</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44900</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45079</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45126</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45145</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45210</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45215</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45217</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45233</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45237</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45245</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>43334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>43342</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>43363</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43402</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43404</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43409</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43419</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43423</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43430</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43431</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43433</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43437</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43444</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43447</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43451</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43453</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43472</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43476</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>43490</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>43496</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>43501</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>43521</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>43523</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>43529</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43537</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43601</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43602</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43605</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>43616</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>43619</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>43622</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>43626</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43630</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43640</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43641</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>43643</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43656</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43657</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43661</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43662</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43671</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>43678</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>43682</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>43684</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43689</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>43696</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43699</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>43705</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43707</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>43712</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>43717</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>43725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>43738</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43739</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43740</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43745</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43754</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43760</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43783</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43790</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43791</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43805</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>43808</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>43811</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>43812</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>43833</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>43860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>43871</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>43878</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>43881</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>43888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>43894</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>43909</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>43927</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>43929</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>43940</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>43941</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>43966</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>43976</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>43979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>43985</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44000</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44005</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44007</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44015</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44019</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44027</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44033</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44035</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44036</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44045</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44057</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44062</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44068</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44083</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44084</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44103</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44104</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44123</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44126</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44158</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44160</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44162</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44165</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44168</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44187</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44201</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44203</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44207</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44209</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44218</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44224</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44245</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44251</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44253</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44267</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44277</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44278</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44280</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44284</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44286</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44306</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44314</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44321</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44322</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44336</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44340</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44349</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44350</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44354</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44357</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44358</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44361</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44378</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44384</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44387</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44392</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44397</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44399</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44400</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44417</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44434</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>44435</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44438</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44440</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44441</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44446</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44455</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44459</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44473</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58154,7 +58154,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58211,7 +58211,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58328,14 +58328,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4454-2024</t>
+          <t>A 4522-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -58385,14 +58385,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4561-2024</t>
+          <t>A 4526-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -58442,14 +58442,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4522-2024</t>
+          <t>A 4454-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -58499,14 +58499,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4526-2024</t>
+          <t>A 4561-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -58563,7 +58563,7 @@
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45330</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45331</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44529</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45237</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43609</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>43976</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44019</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44033</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44279</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44602</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44806</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44827</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44840</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44908</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44930</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44966</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44986</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45107</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45237</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>43437</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>43535</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43703</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43705</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>43784</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43812</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44033</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44053</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44293</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44776</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44792</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44791</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44826</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44842</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44900</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45079</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45126</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45145</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45210</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45215</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45217</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45233</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45237</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45245</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>43334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>43342</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>43363</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43402</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43404</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43409</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43419</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43423</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43430</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43431</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43433</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43437</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43444</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43447</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43451</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43453</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43472</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43476</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>43490</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>43496</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>43501</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>43521</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>43523</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>43529</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43537</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43601</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43602</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43605</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>43616</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>43619</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>43622</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>43626</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43630</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43640</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43641</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>43643</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43656</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43657</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43661</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43662</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43671</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>43678</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>43682</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>43684</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43689</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>43696</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43699</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>43705</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43707</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>43712</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>43717</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>43725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>43738</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43739</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43740</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43745</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43754</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43760</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43783</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43790</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43791</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43805</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>43808</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>43811</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>43812</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>43833</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>43860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>43871</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>43878</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>43881</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>43888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>43894</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>43909</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>43927</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>43929</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>43940</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>43941</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>43966</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>43976</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>43979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>43985</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44000</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44005</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44007</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44015</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44019</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44027</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44033</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44035</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44036</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44045</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44057</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44062</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44068</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44083</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44084</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44103</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44104</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44123</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44126</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44158</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44160</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44162</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44165</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44168</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44187</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44201</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44203</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44207</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44209</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44218</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44224</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44245</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44251</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44253</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44267</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44277</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44278</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44280</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44284</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44286</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44306</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44314</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44321</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44322</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44336</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44340</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44349</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44350</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44354</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44357</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44358</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44361</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44378</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44384</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44387</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44392</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44397</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44399</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44400</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44417</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44434</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>44435</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44438</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44440</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44441</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44446</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44455</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44459</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44473</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58154,7 +58154,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58211,7 +58211,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58328,14 +58328,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4522-2024</t>
+          <t>A 4454-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -58385,14 +58385,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4526-2024</t>
+          <t>A 4522-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -58442,14 +58442,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4454-2024</t>
+          <t>A 4526-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -58506,7 +58506,7 @@
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58563,7 +58563,7 @@
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45330</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45331</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z930"/>
+  <dimension ref="A1:Z931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44529</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45237</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43609</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>43976</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44019</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44033</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44279</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44602</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44806</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44827</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44840</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44908</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44930</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44966</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44986</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45107</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45237</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>43437</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>43535</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43703</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43705</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>43784</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43812</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44033</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44053</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44293</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44776</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44792</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44791</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44826</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44842</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44900</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45079</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45126</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45145</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45210</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45215</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45217</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45233</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45237</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45245</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>43334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>43342</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>43363</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43402</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43404</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43409</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43419</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43423</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43430</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43431</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43433</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43437</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43444</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43447</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43451</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43453</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43472</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43476</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>43490</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>43496</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>43501</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>43521</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>43523</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>43529</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43537</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43601</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43602</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43605</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>43616</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>43619</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>43622</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>43626</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43630</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43640</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43641</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>43643</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43656</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43657</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43661</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43662</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43671</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>43678</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>43682</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>43684</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43689</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>43696</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43699</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>43705</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43707</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>43712</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>43717</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>43725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>43738</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43739</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43740</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43745</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43754</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43760</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43783</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43790</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43791</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43805</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>43808</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>43811</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>43812</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>43833</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>43860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>43871</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>43878</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>43881</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>43888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>43894</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>43909</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>43927</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>43929</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>43940</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>43941</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>43966</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>43976</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>43979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>43985</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44000</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44005</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44007</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44015</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44019</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44027</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44033</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44035</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44036</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44045</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44057</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44062</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44068</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44083</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44084</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44103</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44104</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44123</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44126</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44158</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44160</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44162</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44165</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44168</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44187</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44201</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44203</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44207</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44209</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44218</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44224</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44245</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44251</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44253</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44267</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44277</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44278</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44280</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44284</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44286</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44306</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44314</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44321</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44322</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44336</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44340</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44349</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44350</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44354</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44357</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44358</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44361</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44378</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44384</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44387</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44392</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44397</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44399</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44400</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44417</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44434</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>44435</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44438</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44440</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44441</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44446</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44455</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44459</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44473</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58154,7 +58154,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58211,7 +58211,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58328,14 +58328,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4454-2024</t>
+          <t>A 4522-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -58385,14 +58385,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4522-2024</t>
+          <t>A 4526-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -58442,14 +58442,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4526-2024</t>
+          <t>A 4551-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -58506,7 +58506,7 @@
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58556,14 +58556,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4551-2024</t>
+          <t>A 4454-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -58620,7 +58620,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45330</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45331</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58838,17 +58838,17 @@
       </c>
       <c r="R929" s="2" t="inlineStr"/>
     </row>
-    <row r="930">
+    <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 5910-2024</t>
+          <t>A 5911-2024</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -58866,39 +58866,101 @@
         </is>
       </c>
       <c r="G930" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H930" t="n">
+        <v>0</v>
+      </c>
+      <c r="I930" t="n">
+        <v>0</v>
+      </c>
+      <c r="J930" t="n">
+        <v>0</v>
+      </c>
+      <c r="K930" t="n">
+        <v>0</v>
+      </c>
+      <c r="L930" t="n">
+        <v>0</v>
+      </c>
+      <c r="M930" t="n">
+        <v>0</v>
+      </c>
+      <c r="N930" t="n">
+        <v>0</v>
+      </c>
+      <c r="O930" t="n">
+        <v>0</v>
+      </c>
+      <c r="P930" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q930" t="n">
+        <v>0</v>
+      </c>
+      <c r="R930" s="2" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>A 5910-2024</t>
+        </is>
+      </c>
+      <c r="B931" s="1" t="n">
+        <v>45335</v>
+      </c>
+      <c r="C931" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>BERG</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="G931" t="n">
         <v>29.7</v>
       </c>
-      <c r="H930" t="n">
-        <v>0</v>
-      </c>
-      <c r="I930" t="n">
-        <v>0</v>
-      </c>
-      <c r="J930" t="n">
-        <v>0</v>
-      </c>
-      <c r="K930" t="n">
-        <v>0</v>
-      </c>
-      <c r="L930" t="n">
-        <v>0</v>
-      </c>
-      <c r="M930" t="n">
-        <v>0</v>
-      </c>
-      <c r="N930" t="n">
-        <v>0</v>
-      </c>
-      <c r="O930" t="n">
-        <v>0</v>
-      </c>
-      <c r="P930" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q930" t="n">
-        <v>0</v>
-      </c>
-      <c r="R930" s="2" t="inlineStr"/>
+      <c r="H931" t="n">
+        <v>0</v>
+      </c>
+      <c r="I931" t="n">
+        <v>0</v>
+      </c>
+      <c r="J931" t="n">
+        <v>0</v>
+      </c>
+      <c r="K931" t="n">
+        <v>0</v>
+      </c>
+      <c r="L931" t="n">
+        <v>0</v>
+      </c>
+      <c r="M931" t="n">
+        <v>0</v>
+      </c>
+      <c r="N931" t="n">
+        <v>0</v>
+      </c>
+      <c r="O931" t="n">
+        <v>0</v>
+      </c>
+      <c r="P931" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q931" t="n">
+        <v>0</v>
+      </c>
+      <c r="R931" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z931"/>
+  <dimension ref="A1:Z932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44529</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45237</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43609</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>43976</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44019</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44033</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44279</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44602</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44806</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44827</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44840</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44908</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44930</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44966</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44986</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45107</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45237</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>43437</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>43535</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43703</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43705</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>43784</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43812</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44033</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44053</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44293</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44776</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44792</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44791</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44826</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44842</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44900</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45079</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45126</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45145</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45210</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45215</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45217</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45233</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45237</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45245</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>43334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>43342</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>43363</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43402</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43404</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43409</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43419</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43423</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43430</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43431</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43433</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43437</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43444</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43447</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43451</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43453</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43472</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43476</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>43490</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>43496</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>43501</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>43521</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>43523</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>43529</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43537</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43601</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43602</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43605</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>43616</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>43619</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>43622</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>43626</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43630</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43640</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43641</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>43643</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43656</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43657</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43661</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43662</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43671</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>43678</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>43682</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>43684</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43689</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>43696</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43699</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>43705</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43707</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>43712</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>43717</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>43725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>43738</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43739</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43740</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43745</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43754</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43760</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43783</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43790</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43791</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43805</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>43808</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>43811</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>43812</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>43833</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>43860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>43871</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>43878</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>43881</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>43888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>43894</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>43909</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>43927</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>43929</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>43940</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>43941</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>43966</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>43976</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>43979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>43985</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44000</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44005</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44007</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44015</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44019</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44027</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44033</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44035</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44036</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44045</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44057</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44062</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44068</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44083</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44084</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44103</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44104</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44123</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44126</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44158</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44160</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44162</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44165</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44168</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44187</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44201</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44203</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44207</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44209</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44218</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44224</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44245</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44251</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44253</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44267</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44277</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44278</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44280</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44284</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44286</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44306</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44314</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44321</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44322</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44336</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44340</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44349</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44350</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44354</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44357</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44358</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44361</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44378</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44384</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44387</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44392</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44397</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44399</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44400</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44417</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44434</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>44435</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44438</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44440</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44441</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44446</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44455</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44459</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44473</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58154,7 +58154,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58211,7 +58211,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58442,14 +58442,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4551-2024</t>
+          <t>A 4454-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -58506,7 +58506,7 @@
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58556,14 +58556,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4454-2024</t>
+          <t>A 4551-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -58620,7 +58620,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45330</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45331</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -58900,7 +58900,7 @@
       </c>
       <c r="R930" s="2" t="inlineStr"/>
     </row>
-    <row r="931">
+    <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
           <t>A 5910-2024</t>
@@ -58910,7 +58910,7 @@
         <v>45335</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -58961,6 +58961,63 @@
         <v>0</v>
       </c>
       <c r="R931" s="2" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>A 7040-2024</t>
+        </is>
+      </c>
+      <c r="B932" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C932" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>BERG</t>
+        </is>
+      </c>
+      <c r="G932" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H932" t="n">
+        <v>0</v>
+      </c>
+      <c r="I932" t="n">
+        <v>0</v>
+      </c>
+      <c r="J932" t="n">
+        <v>0</v>
+      </c>
+      <c r="K932" t="n">
+        <v>0</v>
+      </c>
+      <c r="L932" t="n">
+        <v>0</v>
+      </c>
+      <c r="M932" t="n">
+        <v>0</v>
+      </c>
+      <c r="N932" t="n">
+        <v>0</v>
+      </c>
+      <c r="O932" t="n">
+        <v>0</v>
+      </c>
+      <c r="P932" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q932" t="n">
+        <v>0</v>
+      </c>
+      <c r="R932" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z932"/>
+  <dimension ref="A1:Z934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44529</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45237</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43609</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>43976</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44019</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44033</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44279</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44602</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44806</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44827</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44840</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44908</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44930</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44966</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44986</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45107</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45237</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>43437</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>43535</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43703</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43705</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>43784</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43812</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44033</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44053</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44293</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44776</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44792</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44791</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44826</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44842</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44900</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45079</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45126</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45145</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45210</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45215</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45217</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45233</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45237</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45245</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>43334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>43342</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>43363</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43402</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43404</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43409</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43419</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43423</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43430</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43431</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43433</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43437</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43444</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43447</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43451</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43453</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43472</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43476</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>43490</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>43496</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>43501</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>43521</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>43523</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>43529</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43537</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43601</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43602</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43605</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>43616</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>43619</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>43622</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>43626</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43630</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43640</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43641</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>43643</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43656</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43657</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43661</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43662</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43671</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>43678</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>43682</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>43684</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43689</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>43696</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43699</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>43705</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43707</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>43712</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>43717</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>43725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>43738</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43739</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43740</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43745</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43754</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43760</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43783</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43790</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43791</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43805</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>43808</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>43811</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>43812</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>43833</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>43860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>43871</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>43878</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>43881</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>43888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>43894</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>43909</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>43927</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>43929</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>43940</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>43941</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>43966</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>43976</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>43979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>43985</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44000</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44005</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44007</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44015</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44019</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44027</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44033</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44035</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44036</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44045</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44057</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44062</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44068</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44083</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44084</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44103</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44104</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44123</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44126</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44158</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44160</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44162</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44165</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44168</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44187</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44201</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44203</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44207</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44209</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44218</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44224</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44245</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44251</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44253</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44267</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44277</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44278</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44280</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44284</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44286</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44306</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44314</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44321</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44322</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44336</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44340</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44349</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44350</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44354</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44357</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44358</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44361</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44378</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44384</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44387</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44392</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44397</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44399</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44400</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44417</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44434</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>44435</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44438</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44440</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44441</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44446</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44455</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44459</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44473</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57976,14 +57976,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 2664-2024</t>
+          <t>A 2679-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -57996,7 +57996,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -58033,14 +58033,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 2679-2024</t>
+          <t>A 2664-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58053,7 +58053,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -58097,7 +58097,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58154,7 +58154,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58211,7 +58211,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58328,14 +58328,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4522-2024</t>
+          <t>A 4561-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>0.6</v>
+        <v>7.4</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -58385,14 +58385,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4526-2024</t>
+          <t>A 4454-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -58442,14 +58442,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4454-2024</t>
+          <t>A 4522-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -58499,14 +58499,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4561-2024</t>
+          <t>A 4526-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -58563,7 +58563,7 @@
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45330</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45331</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45335</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -58962,7 +58962,7 @@
       </c>
       <c r="R931" s="2" t="inlineStr"/>
     </row>
-    <row r="932">
+    <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
           <t>A 7040-2024</t>
@@ -58972,7 +58972,7 @@
         <v>45343</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -59018,6 +59018,120 @@
         <v>0</v>
       </c>
       <c r="R932" s="2" t="inlineStr"/>
+    </row>
+    <row r="933" ht="15" customHeight="1">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>A 7195-2024</t>
+        </is>
+      </c>
+      <c r="B933" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C933" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>BERG</t>
+        </is>
+      </c>
+      <c r="G933" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H933" t="n">
+        <v>0</v>
+      </c>
+      <c r="I933" t="n">
+        <v>0</v>
+      </c>
+      <c r="J933" t="n">
+        <v>0</v>
+      </c>
+      <c r="K933" t="n">
+        <v>0</v>
+      </c>
+      <c r="L933" t="n">
+        <v>0</v>
+      </c>
+      <c r="M933" t="n">
+        <v>0</v>
+      </c>
+      <c r="N933" t="n">
+        <v>0</v>
+      </c>
+      <c r="O933" t="n">
+        <v>0</v>
+      </c>
+      <c r="P933" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q933" t="n">
+        <v>0</v>
+      </c>
+      <c r="R933" s="2" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>A 7192-2024</t>
+        </is>
+      </c>
+      <c r="B934" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C934" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>BERG</t>
+        </is>
+      </c>
+      <c r="G934" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H934" t="n">
+        <v>0</v>
+      </c>
+      <c r="I934" t="n">
+        <v>0</v>
+      </c>
+      <c r="J934" t="n">
+        <v>0</v>
+      </c>
+      <c r="K934" t="n">
+        <v>0</v>
+      </c>
+      <c r="L934" t="n">
+        <v>0</v>
+      </c>
+      <c r="M934" t="n">
+        <v>0</v>
+      </c>
+      <c r="N934" t="n">
+        <v>0</v>
+      </c>
+      <c r="O934" t="n">
+        <v>0</v>
+      </c>
+      <c r="P934" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q934" t="n">
+        <v>0</v>
+      </c>
+      <c r="R934" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z934"/>
+  <dimension ref="A1:Z935"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44529</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45237</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43609</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>43976</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44019</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44033</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44279</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44602</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44806</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44827</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44840</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44908</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44930</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44966</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44986</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45107</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45237</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>43437</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>43535</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43703</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43705</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>43784</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43812</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44033</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44053</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44293</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44776</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44792</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44791</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44826</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44842</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44900</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45079</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45126</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45145</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45210</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45215</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45217</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45233</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45237</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45245</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>43334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>43342</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>43363</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43402</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43404</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43409</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43419</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43423</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43430</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43431</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43433</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43437</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43444</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43447</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43451</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43453</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43472</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43476</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>43490</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>43496</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>43501</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>43521</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>43523</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>43529</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43537</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43601</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43602</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43605</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>43616</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>43619</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>43622</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>43626</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43630</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43640</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43641</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>43643</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43656</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43657</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43661</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43662</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43671</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>43678</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>43682</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>43684</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43689</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>43696</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43699</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>43705</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43707</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>43712</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>43717</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>43725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>43738</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43739</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43740</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43745</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43754</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43760</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43783</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43790</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43791</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43805</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>43808</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>43811</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>43812</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>43833</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>43860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>43871</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>43878</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>43881</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>43888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>43894</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>43909</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>43927</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>43929</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>43940</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>43941</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>43966</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>43976</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>43979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>43985</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44000</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44005</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44007</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44015</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44019</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44027</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44033</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44035</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44036</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44045</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44057</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44062</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44068</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44083</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44084</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44103</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44104</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44123</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44126</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44158</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44160</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44162</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44165</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44168</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44187</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44201</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44203</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44207</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44209</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44218</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44224</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44245</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44251</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44253</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44267</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44277</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44278</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44280</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44284</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44286</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44306</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44314</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44321</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44322</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44336</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44340</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44349</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44350</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44354</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44357</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44358</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44361</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44378</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44384</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44387</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44392</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44397</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44399</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44400</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44417</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44434</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>44435</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44438</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44440</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44441</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44446</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44455</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44459</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44473</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58154,7 +58154,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58211,7 +58211,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58328,14 +58328,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4561-2024</t>
+          <t>A 4522-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>7.4</v>
+        <v>0.6</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -58385,14 +58385,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4454-2024</t>
+          <t>A 4526-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -58442,14 +58442,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4522-2024</t>
+          <t>A 4454-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -58499,14 +58499,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4526-2024</t>
+          <t>A 4551-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -58556,14 +58556,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4551-2024</t>
+          <t>A 4561-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -58620,7 +58620,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45330</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45331</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58841,14 +58841,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 5911-2024</t>
+          <t>A 5910-2024</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -58866,7 +58866,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>28.6</v>
+        <v>29.7</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -58903,14 +58903,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 5910-2024</t>
+          <t>A 5911-2024</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -58928,7 +58928,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>29.7</v>
+        <v>28.6</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -58972,7 +58972,7 @@
         <v>45343</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -59029,7 +59029,7 @@
         <v>45344</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -59076,7 +59076,7 @@
       </c>
       <c r="R933" s="2" t="inlineStr"/>
     </row>
-    <row r="934">
+    <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
           <t>A 7192-2024</t>
@@ -59086,7 +59086,7 @@
         <v>45344</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -59132,6 +59132,63 @@
         <v>0</v>
       </c>
       <c r="R934" s="2" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>A 7377-2024</t>
+        </is>
+      </c>
+      <c r="B935" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C935" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>JÄMTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>BERG</t>
+        </is>
+      </c>
+      <c r="G935" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H935" t="n">
+        <v>0</v>
+      </c>
+      <c r="I935" t="n">
+        <v>0</v>
+      </c>
+      <c r="J935" t="n">
+        <v>0</v>
+      </c>
+      <c r="K935" t="n">
+        <v>0</v>
+      </c>
+      <c r="L935" t="n">
+        <v>0</v>
+      </c>
+      <c r="M935" t="n">
+        <v>0</v>
+      </c>
+      <c r="N935" t="n">
+        <v>0</v>
+      </c>
+      <c r="O935" t="n">
+        <v>0</v>
+      </c>
+      <c r="P935" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q935" t="n">
+        <v>0</v>
+      </c>
+      <c r="R935" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44529</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45237</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43609</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>43976</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44019</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44033</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44279</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44602</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44806</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44827</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44840</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44908</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44930</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44966</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44986</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45107</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45237</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>43437</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>43535</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43703</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43705</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>43784</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43812</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44033</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44053</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44293</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44776</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44792</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44791</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44826</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44842</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44900</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45079</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45126</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45145</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45210</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45215</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45217</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45233</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45237</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45245</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>43334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>43342</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>43363</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43402</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43404</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43409</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43419</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43423</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43430</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43431</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43433</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43437</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43444</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43447</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43451</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43453</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43472</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43476</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>43490</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>43496</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>43501</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>43521</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>43523</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>43529</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43537</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43601</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43602</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43605</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>43616</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>43619</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>43622</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>43626</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43630</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43640</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43641</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>43643</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43656</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43657</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43661</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43662</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43671</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>43678</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>43682</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>43684</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43689</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>43696</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43699</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>43705</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43707</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>43712</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>43717</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>43725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>43738</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43739</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43740</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43745</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43754</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43760</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43783</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43790</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43791</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43805</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>43808</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>43811</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>43812</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>43833</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>43860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>43871</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>43878</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>43881</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>43888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>43894</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>43909</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>43927</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>43929</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>43940</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>43941</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>43966</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>43976</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>43979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>43985</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44000</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44005</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44007</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44015</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44019</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44027</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44033</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44035</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44036</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44045</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44057</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44062</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44068</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44083</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44084</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44103</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44104</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44123</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44126</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44158</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44160</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44162</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44165</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44168</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44187</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44201</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44203</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44207</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44209</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44218</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44224</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44245</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44251</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44253</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44267</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44277</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44278</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44280</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44284</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44286</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44306</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44314</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44321</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44322</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44336</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44340</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44349</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44350</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44354</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44357</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44358</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44361</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44378</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44384</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44387</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44392</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44397</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44399</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44400</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44417</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44434</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>44435</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44438</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44440</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44441</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44446</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44455</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44459</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44473</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58154,7 +58154,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58211,7 +58211,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58449,7 +58449,7 @@
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58499,14 +58499,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4551-2024</t>
+          <t>A 4561-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -58556,14 +58556,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4561-2024</t>
+          <t>A 4551-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -58620,7 +58620,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45330</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45331</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45335</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45343</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -59022,14 +59022,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 7195-2024</t>
+          <t>A 7192-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -59042,7 +59042,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -59079,14 +59079,14 @@
     <row r="934" ht="15" customHeight="1">
       <c r="A934" t="inlineStr">
         <is>
-          <t>A 7192-2024</t>
+          <t>A 7195-2024</t>
         </is>
       </c>
       <c r="B934" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -59099,7 +59099,7 @@
         </is>
       </c>
       <c r="G934" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="H934" t="n">
         <v>0</v>
@@ -59143,7 +59143,7 @@
         <v>45345</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44529</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45237</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43609</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>43976</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44019</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44033</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44279</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44602</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44806</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44827</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44840</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44908</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44930</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44966</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44986</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45107</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45237</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>43437</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>43535</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43703</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43705</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>43784</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43812</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44033</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44053</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44293</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44776</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44792</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44791</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44826</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44842</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44900</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45079</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45126</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45145</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45210</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45215</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45217</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45233</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45237</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45245</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>43334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>43342</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>43363</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43402</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43404</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43409</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43419</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43423</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43430</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43431</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43433</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43437</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43444</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43447</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43451</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43453</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43472</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43476</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>43490</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>43496</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>43501</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>43521</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>43523</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>43529</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43537</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43601</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43602</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43605</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>43616</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>43619</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>43622</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>43626</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43630</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43640</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43641</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>43643</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43656</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43657</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43661</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43662</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43671</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>43678</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>43682</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>43684</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43689</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>43696</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43699</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>43705</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43707</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>43712</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>43717</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>43725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>43738</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43739</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43740</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43745</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43754</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43760</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43783</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43790</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43791</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43805</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>43808</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>43811</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>43812</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>43833</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>43860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>43871</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>43878</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>43881</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>43888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>43894</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>43909</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>43927</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>43929</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>43940</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>43941</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>43966</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>43976</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>43979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>43985</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44000</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44005</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44007</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44015</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44019</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44027</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44033</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44035</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44036</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44045</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44057</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44062</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44068</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44083</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44084</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44103</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44104</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44123</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44126</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44158</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44160</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44162</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44165</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44168</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44187</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44201</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44203</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44207</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44209</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44218</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44224</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44245</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44251</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44253</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44267</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44277</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44278</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44280</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44284</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44286</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44306</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44314</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44321</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44322</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44336</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44340</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44349</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44350</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44354</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44357</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44358</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44361</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44378</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44384</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44387</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44392</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44397</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44399</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44400</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44417</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44434</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>44435</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44438</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44440</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44441</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44446</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44455</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44459</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44473</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58154,7 +58154,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58211,7 +58211,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58449,7 +58449,7 @@
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58499,14 +58499,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 4561-2024</t>
+          <t>A 4551-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -58556,14 +58556,14 @@
     <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
-          <t>A 4551-2024</t>
+          <t>A 4561-2024</t>
         </is>
       </c>
       <c r="B925" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         </is>
       </c>
       <c r="G925" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -58620,7 +58620,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58670,14 +58670,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 5215-2024</t>
+          <t>A 5264-2024</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
-        <v>45330</v>
+        <v>45331</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -58727,14 +58727,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 5264-2024</t>
+          <t>A 5215-2024</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
-        <v>45331</v>
+        <v>45330</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -58791,7 +58791,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45335</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45343</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -59029,7 +59029,7 @@
         <v>45344</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>45344</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>45345</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44529</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45237</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>43433</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>43609</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>43976</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44019</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44033</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44279</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>44463</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44602</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44806</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44827</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44840</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44908</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44930</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44966</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44986</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>45107</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>45209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45237</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>43437</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>43535</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>43703</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43705</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>43784</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43812</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>44033</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44053</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44293</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44529</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>44776</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44792</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44791</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44826</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>44842</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44861</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44900</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45079</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45126</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45145</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45210</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45215</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45217</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45233</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45237</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45245</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>43334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>43342</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>43363</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>43389</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>43402</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>43404</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>43409</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>43419</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>43423</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>43430</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>43431</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>43433</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>43437</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>43444</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>43447</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>43448</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>43451</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>43453</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
         <v>43455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>43472</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>43476</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>43490</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>43496</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>43501</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>43521</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>43523</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>43529</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>43537</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>43556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>43601</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>43602</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>43605</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>43607</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>43608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>43616</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>43619</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>43622</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>43626</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>43629</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43630</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43640</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43641</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>43643</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>43656</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>43657</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>43661</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>43662</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>43671</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>43678</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>43682</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>43684</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>43689</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>43696</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43699</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>43705</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>43707</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>43712</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>43717</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>43725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>43738</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>43739</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>43740</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>43745</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>43747</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>43754</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>43760</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>43770</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>43783</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>43790</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>43791</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>43805</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>43808</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>43811</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>43812</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>43833</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>43844</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>43860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>43866</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>43871</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>43878</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>43881</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>43888</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>43894</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>43909</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>43927</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>43929</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>43940</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>43941</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>43966</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>43976</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>43979</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>43985</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44000</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44005</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>44007</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44015</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44019</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44027</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>44033</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44035</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44036</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44045</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>44057</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>44062</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44068</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44083</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44084</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44095</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44103</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44104</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44123</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>44126</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44130</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44158</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44160</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44162</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44165</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44168</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44187</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>44201</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>44203</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44207</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44209</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44218</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44224</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44245</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44251</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44253</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44267</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>44277</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44278</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>44280</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44284</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44286</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>44293</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44306</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>44314</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>44321</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44322</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>44336</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44340</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44349</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44350</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>44354</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>44357</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44358</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44361</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44378</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>44384</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44387</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44392</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44397</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>44399</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44400</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44417</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44434</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24934,7 +24934,7 @@
         <v>44435</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44438</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44440</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44441</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44446</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44455</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44459</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44473</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31689,7 +31689,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31870,7 +31870,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35167,7 +35167,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35224,7 +35224,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35576,7 +35576,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36047,7 +36047,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38808,7 +38808,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41480,7 +41480,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41961,7 +41961,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42080,7 +42080,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44351,7 +44351,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45318,7 +45318,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45789,7 +45789,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47951,7 +47951,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48799,7 +48799,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48918,7 +48918,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51960,7 +51960,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53239,7 +53239,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53586,7 +53586,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53814,7 +53814,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54042,7 +54042,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54270,7 +54270,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54674,7 +54674,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54912,7 +54912,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55031,7 +55031,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55150,7 +55150,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55207,7 +55207,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55264,7 +55264,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55378,7 +55378,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55549,7 +55549,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56414,7 +56414,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56771,7 +56771,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57869,7 +57869,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57983,7 +57983,7 @@
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58040,7 +58040,7 @@
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58154,7 +58154,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58211,7 +58211,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58328,14 +58328,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 4522-2024</t>
+          <t>A 4454-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -58385,14 +58385,14 @@
     <row r="922" ht="15" customHeight="1">
       <c r="A922" t="inlineStr">
         <is>
-          <t>A 4526-2024</t>
+          <t>A 4522-2024</t>
         </is>
       </c>
       <c r="B922" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         </is>
       </c>
       <c r="G922" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -58442,14 +58442,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 4454-2024</t>
+          <t>A 4526-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -58506,7 +58506,7 @@
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58563,7 +58563,7 @@
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45331</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45330</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58841,14 +58841,14 @@
     <row r="930" ht="15" customHeight="1">
       <c r="A930" t="inlineStr">
         <is>
-          <t>A 5910-2024</t>
+          <t>A 5911-2024</t>
         </is>
       </c>
       <c r="B930" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -58866,7 +58866,7 @@
         </is>
       </c>
       <c r="G930" t="n">
-        <v>29.7</v>
+        <v>28.6</v>
       </c>
       <c r="H930" t="n">
         <v>0</v>
@@ -58903,14 +58903,14 @@
     <row r="931" ht="15" customHeight="1">
       <c r="A931" t="inlineStr">
         <is>
-          <t>A 5911-2024</t>
+          <t>A 5910-2024</t>
         </is>
       </c>
       <c r="B931" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -58928,7 +58928,7 @@
         </is>
       </c>
       <c r="G931" t="n">
-        <v>28.6</v>
+        <v>29.7</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -58972,7 +58972,7 @@
         <v>45343</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -59029,7 +59029,7 @@
         <v>45344</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>45344</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>45345</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44473</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44529</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45237</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>43609</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>43976</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44019</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44033</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44148</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>44279</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44463</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44602</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44806</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44827</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44840</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>44908</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44930</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>44966</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>44986</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>45107</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45209</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45237</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>45238</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43437</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43535</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43703</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>43705</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>43784</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43812</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>44033</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>44053</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44293</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44377</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44776</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>44792</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44791</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>44826</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44833</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44842</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44861</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44875</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44900</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45079</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45126</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>45145</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45210</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45215</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>45217</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45222</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45233</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45237</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45245</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>43334</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>43342</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>43363</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>43389</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>43402</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>43404</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>43409</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>43419</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>43423</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>43430</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>43431</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43433</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43437</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43444</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43447</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>43448</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>43453</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43454</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43455</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43472</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43476</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>43490</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>43496</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>43501</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>43521</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>43523</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>43529</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>43537</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>43556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43579</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43601</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43602</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43605</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>43607</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>43608</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43616</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>43619</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>43622</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43626</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>43630</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43641</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>43643</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>43656</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>43657</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43661</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>43671</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43678</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>43682</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>43684</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>43689</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>43696</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>43699</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>43705</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43707</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>43712</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>43717</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>43725</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>43738</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>43739</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>43740</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>43745</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>43747</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>43754</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>43760</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>43770</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>43783</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>43790</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>43791</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>43805</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>43808</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>43811</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>43812</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>43833</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43844</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>43860</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>43866</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>43871</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>43878</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>43881</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>43888</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>43894</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>43909</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>43927</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>43929</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>43940</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>43941</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>43949</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>43976</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>43979</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>43985</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44000</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>44005</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44007</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44015</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44019</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44027</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44033</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44035</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44036</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44045</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44057</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44062</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>44063</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>44068</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44083</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44084</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>44095</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44103</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>44104</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44123</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44126</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44130</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>44158</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>44160</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44162</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>44165</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>44168</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>44187</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>44201</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>44203</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44207</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>44209</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>44218</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>44224</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44245</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44251</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44253</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44267</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44277</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44278</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>44280</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44284</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>44286</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>44293</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>44306</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>44314</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>44321</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>44322</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>44336</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>44340</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>44349</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44350</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44354</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44357</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44358</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>44361</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44378</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>44384</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>44387</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>44389</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>44392</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44397</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44399</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>44400</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44417</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44434</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44435</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44438</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44440</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44441</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44445</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44446</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44455</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44459</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44462</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43956,7 +43956,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47514,7 +47514,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48285,7 +48285,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49361,7 +49361,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51255,7 +51255,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51498,7 +51498,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51622,7 +51622,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51746,7 +51746,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51870,7 +51870,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52279,7 +52279,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52398,7 +52398,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52641,7 +52641,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52926,7 +52926,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54532,7 +54532,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55355,7 +55355,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55640,7 +55640,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>45279</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -55811,7 +55811,7 @@
         <v>45279</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -55868,7 +55868,7 @@
         <v>45279</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55925,7 +55925,7 @@
         <v>45279</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>45279</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -56039,7 +56039,7 @@
         <v>45279</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -56096,7 +56096,7 @@
         <v>45279</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>45279</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>45279</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45280</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -56329,7 +56329,7 @@
         <v>45280</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>45280</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -56448,7 +56448,7 @@
         <v>45280</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -56510,7 +56510,7 @@
         <v>45280</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>45281</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45282</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -56691,7 +56691,7 @@
         <v>45282</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>45282</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>45289</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>45289</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -56919,7 +56919,7 @@
         <v>45290</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56976,7 +56976,7 @@
         <v>45289</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -57033,7 +57033,7 @@
         <v>45289</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -57090,7 +57090,7 @@
         <v>45289</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -57147,7 +57147,7 @@
         <v>45289</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>45293</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>45293</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -57318,7 +57318,7 @@
         <v>45294</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45294</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>45294</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -57504,7 +57504,7 @@
         <v>45299</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>45306</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45306</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -57675,7 +57675,7 @@
         <v>45307</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -57732,7 +57732,7 @@
         <v>45307</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -57789,7 +57789,7 @@
         <v>45307</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -57846,7 +57846,7 @@
         <v>45307</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>45307</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57960,7 +57960,7 @@
         <v>45309</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -58017,7 +58017,7 @@
         <v>45314</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>45314</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -58131,7 +58131,7 @@
         <v>45317</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -58188,7 +58188,7 @@
         <v>45320</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -58245,7 +58245,7 @@
         <v>45320</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -58307,7 +58307,7 @@
         <v>45321</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -58369,7 +58369,7 @@
         <v>45327</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -58426,7 +58426,7 @@
         <v>45327</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -58483,7 +58483,7 @@
         <v>45327</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -58540,7 +58540,7 @@
         <v>45327</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>45327</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -58654,7 +58654,7 @@
         <v>45329</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -58704,14 +58704,14 @@
     <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 5215-2024</t>
+          <t>A 5264-2024</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
-        <v>45330</v>
+        <v>45331</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         </is>
       </c>
       <c r="G927" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -58761,14 +58761,14 @@
     <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
-          <t>A 5264-2024</t>
+          <t>A 5215-2024</t>
         </is>
       </c>
       <c r="B928" s="1" t="n">
-        <v>45331</v>
+        <v>45330</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         </is>
       </c>
       <c r="G928" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -58825,7 +58825,7 @@
         <v>45334</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -58882,7 +58882,7 @@
         <v>45335</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -58944,7 +58944,7 @@
         <v>45335</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -58999,14 +58999,14 @@
     <row r="932" ht="15" customHeight="1">
       <c r="A932" t="inlineStr">
         <is>
-          <t>A 7192-2024</t>
+          <t>A 7195-2024</t>
         </is>
       </c>
       <c r="B932" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -59019,7 +59019,7 @@
         </is>
       </c>
       <c r="G932" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="H932" t="n">
         <v>0</v>
@@ -59056,14 +59056,14 @@
     <row r="933" ht="15" customHeight="1">
       <c r="A933" t="inlineStr">
         <is>
-          <t>A 7195-2024</t>
+          <t>A 7192-2024</t>
         </is>
       </c>
       <c r="B933" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -59076,7 +59076,7 @@
         </is>
       </c>
       <c r="G933" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -59120,7 +59120,7 @@
         <v>45345</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -59177,7 +59177,7 @@
         <v>45349</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z935"/>
+  <dimension ref="A1:Z943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45110</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>43672</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>44375</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45145</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>43395</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>43809</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>44853</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>44799</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45062</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>44354</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45253</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>44578</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45180</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44253</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45222</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>44123</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45132</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>43879</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>44293</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>44376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>44806</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45091</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>44293</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>44477</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44776</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44806</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>44062</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44477</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44883</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44953</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45233</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45238</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>43426</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>43948</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44050</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44474</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44607</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44712</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44799</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>44806</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44967</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45058</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45078</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45289</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>43496</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>44111</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44279</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44293</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44473</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44529</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45237</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45237</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>43433</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>43609</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>43976</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44019</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44033</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44148</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>44279</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44463</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44602</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44806</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44827</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44840</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>44908</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44930</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>44966</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>44986</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>45107</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45209</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45237</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>45238</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43437</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>43535</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>43535</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43703</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>43705</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>43784</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>43812</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>44033</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>44053</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44293</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44377</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44529</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44776</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>44792</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44791</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>44826</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>44833</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44842</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44861</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44875</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44900</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45079</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45126</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>45145</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45210</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45210</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45210</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>45215</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>45217</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45222</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45233</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45233</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>45237</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45245</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>43334</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>43342</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>43363</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>43389</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>43402</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>43402</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>43404</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>43409</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>43409</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>43419</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>43423</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>43430</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>43431</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>43433</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>43433</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>43437</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>43444</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43447</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>43448</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>43448</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43448</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>43448</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>43448</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>43448</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>43451</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>43453</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>43453</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>43453</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>43453</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>43454</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>43454</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>43454</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>43455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>43455</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>43472</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>43476</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>43490</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>43496</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>43501</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>43521</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>43523</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>43529</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>43537</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>43556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>43579</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>43601</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>43602</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>43605</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>43607</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>43608</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43616</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>43619</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>43622</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>43626</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>43629</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>43630</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>43640</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>43640</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>43641</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>43643</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>43643</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>43643</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>43643</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>43656</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>43656</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>43657</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>43661</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>43662</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>43671</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43678</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>43682</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>43684</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>43689</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>43689</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>43689</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>43696</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>43696</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>43696</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>43696</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>43699</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>43705</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43707</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>43712</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>43712</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>43717</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>43725</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>43738</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>43738</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>43739</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>43740</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>43745</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>43747</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>43754</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>43760</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>43760</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>43770</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>43770</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>43783</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>43783</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>43790</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>43791</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>43805</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>43808</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>43808</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>43811</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>43811</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>43812</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>43833</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>43844</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>43844</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>43860</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>43866</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>43871</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>43878</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>43881</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>43881</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>43888</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>43894</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>43894</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>43894</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>43894</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>43909</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>43927</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>43929</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>43940</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>43941</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>43949</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>43976</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>43979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>43979</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>43985</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>43985</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>43985</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>43985</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>43985</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44000</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>44000</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44000</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
         <v>44000</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>44005</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44007</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44015</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44019</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44027</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44033</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44033</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44035</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44036</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44045</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44057</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44062</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>44063</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44063</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>44063</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44063</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>44063</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>44068</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>44083</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44084</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>44095</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>44095</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>44095</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>44095</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>44103</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>44104</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44123</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44123</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44123</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44123</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44123</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44126</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44130</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>44158</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>44160</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>44160</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>44162</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44162</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>44165</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44168</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>44168</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>44187</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>44187</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>44201</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44203</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>44203</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44207</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44209</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>44209</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>44209</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>44209</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>44218</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>44224</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44245</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44251</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44253</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44267</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>44277</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>44277</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44277</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>44277</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44278</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>44280</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44284</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>44286</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>44293</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>44293</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>44293</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>44293</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>44293</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>44306</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>44306</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>44314</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>44321</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>44322</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>44322</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>44336</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>44340</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>44349</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>44349</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>44350</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44350</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44354</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44357</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>44358</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>44361</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44378</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>44384</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>44387</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>44389</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>44392</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44397</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44399</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>44399</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>44399</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44399</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>44400</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44417</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44434</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44435</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44438</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44440</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>44441</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>44445</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>44446</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>44446</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44455</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>44459</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44462</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>44477</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44477</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>44487</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44487</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>44487</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44487</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>44490</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44490</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>44503</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>44512</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44529</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44529</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44529</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44529</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>44530</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44536</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>44536</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>44536</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>44540</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>44543</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>44543</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44545</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44546</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>44551</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44564</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>44564</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>44572</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>44572</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44573</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>44575</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>44575</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44575</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>44575</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>44575</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>44575</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44587</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44587</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>44587</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>44594</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44602</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44606</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>44610</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>44613</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>44615</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>44638</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>44648</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>44648</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>44655</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>44680</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44681</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>44685</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>44687</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>44691</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>44694</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>44694</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>44695</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>44699</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>44704</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29752,7 +29752,7 @@
         <v>44704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44705</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>44705</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>44705</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>44706</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44706</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>44706</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>44712</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>44712</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>44714</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44716</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>44721</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>44725</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>44726</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>44727</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>44730</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>44730</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44729</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44733</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44734</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>44735</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44740</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44739</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>44740</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44740</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44742</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44743</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44748</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44753</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44757</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44764</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44774</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44774</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>44775</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44776</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>44775</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>44776</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>44776</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>44779</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44781</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44783</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44785</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44786</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>44792</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>44791</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>44796</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>44797</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>44800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>44802</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>44803</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>44806</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>44810</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>44810</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>44823</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44823</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>44824</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>44824</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44825</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44834</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44834</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>44837</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>44840</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44839</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44841</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>44845</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>44845</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33917,7 +33917,7 @@
         <v>44845</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>44846</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>44846</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>44847</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>44847</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44851</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>44853</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>44853</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>44853</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>44853</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44853</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>44855</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>44855</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>44855</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>44859</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>44861</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44860</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44862</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44863</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>44866</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>44866</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>44872</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>44874</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>44875</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>44875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>44879</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44887</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44895</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>44895</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>44897</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>44900</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44901</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>44901</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>44902</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>44902</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>44902</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>44903</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>44903</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -36138,7 +36138,7 @@
         <v>44903</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>44903</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>44903</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>44908</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44908</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>44907</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>44907</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>44907</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>44908</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>44908</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>44908</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>44909</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>44909</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>44909</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>44909</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>44911</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>44911</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>44911</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>44914</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>44914</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -37283,7 +37283,7 @@
         <v>44915</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>44916</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>44917</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>44917</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>44918</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>44923</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>44923</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>44923</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44924</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>44924</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>44929</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>44942</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>44951</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>44965</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>44965</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>44966</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>44966</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>44966</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>44973</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>44974</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>44977</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44977</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>44978</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>44979</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>44980</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44980</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44980</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>44984</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>44986</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>44986</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>44987</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>44987</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>44987</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>44987</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>44994</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>44994</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>44994</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>44998</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>44999</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45001</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>45008</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45008</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45009</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45009</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>45009</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45014</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45016</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45021</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45027</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45028</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45028</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45040</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45042</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>45042</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45048</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45050</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45050</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45050</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45058</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45060</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45064</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>45063</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>45072</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45073</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>45078</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45079</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45080</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45082</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45082</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45082</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41457,7 +41457,7 @@
         <v>45086</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41514,7 +41514,7 @@
         <v>45091</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45091</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>45091</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45091</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>45093</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45092</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>45096</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45097</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45097</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45097</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45098</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>45098</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45100</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>45099</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45106</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42486,7 +42486,7 @@
         <v>45111</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>45114</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45119</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45119</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>45119</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45119</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45119</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45120</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45125</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45127</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45127</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>45131</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>45131</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45140</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45142</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45147</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         <v>45148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45149</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45153</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45154</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45156</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45155</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         <v>45158</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>45160</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45161</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43956,7 +43956,7 @@
         <v>45163</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>45163</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>45162</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>45163</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45165</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>45166</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>45167</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45169</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45169</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45171</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45170</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>45170</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45170</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45171</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45170</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45170</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45170</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45171</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45176</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45176</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45176</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45176</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45177</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45181</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45181</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45181</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45182</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45182</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45182</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>45182</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45182</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>45182</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45183</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45184</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45187</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45187</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>45187</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>45188</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45196</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45196</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45196</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>45196</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>45196</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>45196</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45198</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45198</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45200</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45200</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45200</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45200</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45202</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45202</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45202</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47514,7 +47514,7 @@
         <v>45202</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>45202</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47628,7 +47628,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45203</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>45204</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45205</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45205</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45205</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45205</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>45206</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45206</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45208</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45208</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -48285,7 +48285,7 @@
         <v>45209</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -48399,7 +48399,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48570,7 +48570,7 @@
         <v>45209</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45210</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45210</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45210</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45210</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>45210</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>45212</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45215</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45217</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45217</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>45217</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -49361,7 +49361,7 @@
         <v>45217</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45217</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45219</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>45219</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49589,7 +49589,7 @@
         <v>45219</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>45221</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>45221</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>45222</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45222</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45222</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45223</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45224</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45224</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45224</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45226</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>45230</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45231</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
         <v>45231</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>45231</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45233</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>45233</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         <v>45233</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
         <v>45233</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45236</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>45236</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -51255,7 +51255,7 @@
         <v>45236</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>45237</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45237</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51498,7 +51498,7 @@
         <v>45237</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>45237</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51622,7 +51622,7 @@
         <v>45237</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>45237</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51746,7 +51746,7 @@
         <v>45237</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45238</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51870,7 +51870,7 @@
         <v>45238</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
         <v>45237</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>45238</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -52108,7 +52108,7 @@
         <v>45240</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45240</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45240</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -52279,7 +52279,7 @@
         <v>45240</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>45246</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -52398,7 +52398,7 @@
         <v>45247</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>45251</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45251</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45252</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52641,7 +52641,7 @@
         <v>45252</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45252</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>45252</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>45252</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52869,7 +52869,7 @@
         <v>45252</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52926,7 +52926,7 @@
         <v>45253</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45253</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45254</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45255</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45258</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45258</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45259</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45259</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45259</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>45259</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45259</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45260</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45260</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45264</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45264</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45264</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45264</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45264</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45264</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45265</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45265</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45265</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45266</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45266</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -54532,7 +54532,7 @@
         <v>45266</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45266</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45266</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45267</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45267</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45268</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45268</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45268</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>45271</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45271</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -55127,7 +55127,7 @@
         <v>45272</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -55184,7 +55184,7 @@
         <v>45275</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>45275</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45278</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -55355,7 +55355,7 @@
         <v>45278</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>45278</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -55469,7 +55469,7 @@
         <v>45278</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>45278</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45279</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -55640,7 +55640,7 @@
         <v>45279</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45279</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
  